--- a/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
+++ b/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="153">
   <si>
     <t>name</t>
   </si>
@@ -455,9 +455,6 @@
   </si>
   <si>
     <t>IT0 1</t>
-  </si>
-  <si>
-    <t>Al/St 240/40 4-bundle 380.0</t>
   </si>
   <si>
     <t>StorageUnit</t>
@@ -1201,7 +1198,7 @@
     </row>
     <row r="4" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -1299,7 +1296,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
@@ -1415,111 +1412,6 @@
       </c>
       <c r="AJ1" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="5">
-        <v>26.722486799397799</v>
-      </c>
-      <c r="F2" s="5">
-        <v>3.2588399750153099</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1.6954233582923101E-2</v>
-      </c>
-      <c r="I2">
-        <v>10188.6156704431</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2">
-        <v>10188.6156704431</v>
-      </c>
-      <c r="M2">
-        <v>30188.615670443101</v>
-      </c>
-      <c r="O2">
-        <v>0.7</v>
-      </c>
-      <c r="P2">
-        <v>27379.125882644501</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2">
-        <v>651.76797097769202</v>
-      </c>
-      <c r="U2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <v>6</v>
-      </c>
-      <c r="X2" t="e">
-        <f>-inf</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>380</v>
-      </c>
-      <c r="AI2">
-        <v>2.58</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1972,13 +1864,13 @@
     </row>
     <row r="2" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15" t="s">
@@ -2087,10 +1979,10 @@
     </row>
     <row r="3" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>72</v>
@@ -2227,7 +2119,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2272,7 +2164,7 @@
         <v>3</v>
       </c>
       <c r="P1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q1" t="s">
         <v>18</v>
@@ -2299,16 +2191,16 @@
         <v>39</v>
       </c>
       <c r="Y1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z1" t="s">
         <v>146</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>147</v>
       </c>
       <c r="AA1" t="s">
         <v>34</v>
       </c>
       <c r="AB1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AC1" t="s">
         <v>27</v>
@@ -2323,7 +2215,7 @@
         <v>22</v>
       </c>
       <c r="AG1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH1" t="s">
         <v>61</v>
@@ -2334,7 +2226,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
@@ -2556,10 +2448,10 @@
     </row>
     <row r="2" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15" t="s">

--- a/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
+++ b/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="154">
   <si>
     <t>name</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>IT0 0 H2 Fuel Cell</t>
+  </si>
+  <si>
+    <t>line 0-1</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1299,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
@@ -1412,6 +1415,38 @@
       </c>
       <c r="AJ1" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2">
+        <v>10000</v>
+      </c>
+      <c r="P2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
+++ b/test/configs/data/test/3n_3c_1gext_1h_1bext_2l.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="155">
   <si>
     <t>name</t>
   </si>
@@ -361,9 +361,6 @@
     <t>#6b4c04</t>
   </si>
   <si>
-    <t>gas CHP</t>
-  </si>
-  <si>
     <t>#210af5</t>
   </si>
   <si>
@@ -488,6 +485,12 @@
   </si>
   <si>
     <t>line 0-1</t>
+  </si>
+  <si>
+    <t>CCGT</t>
+  </si>
+  <si>
+    <t>IT0 1 CCGT</t>
   </si>
 </sst>
 </file>
@@ -951,58 +954,58 @@
     </row>
     <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1010,7 +1013,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1018,7 +1021,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1026,12 +1029,12 @@
         <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>110</v>
@@ -1163,7 +1166,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" s="17">
         <v>380</v>
@@ -1201,7 +1204,7 @@
     </row>
     <row r="4" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -1280,13 +1283,13 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>87</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1327,31 +1330,31 @@
         <v>85</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I1" t="s">
         <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
         <v>83</v>
       </c>
       <c r="L1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M1" t="s">
         <v>127</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>128</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>129</v>
-      </c>
-      <c r="O1" t="s">
-        <v>130</v>
       </c>
       <c r="P1" t="s">
         <v>21</v>
@@ -1375,43 +1378,43 @@
         <v>49</v>
       </c>
       <c r="W1" t="s">
+        <v>130</v>
+      </c>
+      <c r="X1" t="s">
         <v>131</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>132</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>133</v>
       </c>
       <c r="Z1" t="s">
         <v>96</v>
       </c>
       <c r="AA1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB1" t="s">
         <v>134</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>135</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>136</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>137</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>138</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>139</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>140</v>
       </c>
       <c r="AH1" t="s">
         <v>88</v>
       </c>
       <c r="AI1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AJ1" t="s">
         <v>64</v>
@@ -1419,13 +1422,13 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" s="5">
         <v>5</v>
@@ -1459,7 +1462,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="5" bestFit="1" customWidth="1"/>
@@ -1719,6 +1722,120 @@
       </c>
       <c r="AM2" s="2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3">
+        <v>4476</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>4476</v>
+      </c>
+      <c r="I3">
+        <v>100000</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="e">
+        <f t="shared" ref="M3" si="0">-inf</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>153</v>
+      </c>
+      <c r="R3">
+        <v>48.527628571428501</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3">
+        <v>110915.226328986</v>
+      </c>
+      <c r="X3">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>4476</v>
+      </c>
+      <c r="AM3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1899,13 +2016,13 @@
     </row>
     <row r="2" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15" t="s">
@@ -2014,10 +2131,10 @@
     </row>
     <row r="3" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>72</v>
@@ -2154,7 +2271,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2199,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="P1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q1" t="s">
         <v>18</v>
@@ -2226,16 +2343,16 @@
         <v>39</v>
       </c>
       <c r="Y1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z1" t="s">
         <v>145</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>146</v>
       </c>
       <c r="AA1" t="s">
         <v>34</v>
       </c>
       <c r="AB1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AC1" t="s">
         <v>27</v>
@@ -2250,7 +2367,7 @@
         <v>22</v>
       </c>
       <c r="AG1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH1" t="s">
         <v>61</v>
@@ -2261,7 +2378,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
@@ -2301,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2483,10 +2600,10 @@
     </row>
     <row r="2" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15" t="s">
